--- a/coverage/data/state_spec_document_portals.xlsx
+++ b/coverage/data/state_spec_document_portals.xlsx
@@ -5865,7 +5865,7 @@
     <t xml:space="preserve">E-bidding: Core $100/mo (1 agency) or Advanced $349/mo (5 agencies); extra agency $35/mo. Online Plan Sheets download add-on $95/mo. Digital ID for bid submission $100 one-time.</t>
   </si>
   <si>
-    <t xml:space="preserve">Free info-only account can browse lettings and view/download letting documents from 40+ agencies. This is the single highest-value free registration.</t>
+    <t xml:space="preserve">CORRECTED (measured 2026-08-06 in live adapter build): no anonymous read path exists; even an info account requires signing in to view letting documents. Treat as account-gated. 12+ DOT states have working adapters without it.</t>
   </si>
   <si>
     <t xml:space="preserve">QuestCDN</t>
@@ -11764,12 +11764,12 @@
   <dimension ref="A1:F51"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11792,7 +11792,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
@@ -11812,7 +11812,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
@@ -11832,7 +11832,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
@@ -11852,7 +11852,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
@@ -11872,7 +11872,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
@@ -11892,7 +11892,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
@@ -11912,7 +11912,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
@@ -11932,7 +11932,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
@@ -11952,7 +11952,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
@@ -11972,7 +11972,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
@@ -11992,7 +11992,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="n">
         <v>11</v>
       </c>
@@ -12012,7 +12012,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
@@ -12032,7 +12032,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="n">
         <v>13</v>
       </c>
@@ -12052,7 +12052,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="n">
         <v>14</v>
       </c>
@@ -12072,7 +12072,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="n">
         <v>15</v>
       </c>
@@ -12092,7 +12092,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
@@ -12112,7 +12112,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="n">
         <v>17</v>
       </c>
@@ -12132,7 +12132,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="n">
         <v>18</v>
       </c>
@@ -12152,7 +12152,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="n">
         <v>19</v>
       </c>
@@ -12172,7 +12172,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="n">
         <v>20</v>
       </c>
@@ -12192,7 +12192,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="n">
         <v>21</v>
       </c>
@@ -12212,7 +12212,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="n">
         <v>22</v>
       </c>
@@ -12232,7 +12232,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="n">
         <v>23</v>
       </c>
@@ -12252,7 +12252,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="n">
         <v>24</v>
       </c>
@@ -12272,7 +12272,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="n">
         <v>25</v>
       </c>
@@ -12292,7 +12292,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="n">
         <v>26</v>
       </c>
@@ -12312,7 +12312,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="n">
         <v>27</v>
       </c>
@@ -12332,7 +12332,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="n">
         <v>28</v>
       </c>
@@ -12352,7 +12352,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="n">
         <v>29</v>
       </c>
@@ -12372,7 +12372,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="n">
         <v>30</v>
       </c>
@@ -12392,7 +12392,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="n">
         <v>31</v>
       </c>
@@ -12412,7 +12412,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="n">
         <v>32</v>
       </c>
@@ -12432,7 +12432,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="n">
         <v>33</v>
       </c>
@@ -12452,7 +12452,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="n">
         <v>34</v>
       </c>
@@ -12472,7 +12472,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="n">
         <v>35</v>
       </c>
@@ -12492,7 +12492,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="n">
         <v>36</v>
       </c>
@@ -12512,7 +12512,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="n">
         <v>37</v>
       </c>
@@ -12532,7 +12532,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="n">
         <v>38</v>
       </c>
@@ -12552,7 +12552,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="n">
         <v>39</v>
       </c>
@@ -12572,7 +12572,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="n">
         <v>40</v>
       </c>
@@ -12592,7 +12592,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="n">
         <v>41</v>
       </c>
@@ -12612,7 +12612,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="n">
         <v>42</v>
       </c>
@@ -12632,7 +12632,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="n">
         <v>43</v>
       </c>
@@ -12652,7 +12652,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="n">
         <v>44</v>
       </c>
@@ -12672,7 +12672,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="n">
         <v>45</v>
       </c>
@@ -12692,7 +12692,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="n">
         <v>46</v>
       </c>
@@ -12712,7 +12712,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="n">
         <v>47</v>
       </c>
@@ -12732,7 +12732,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="n">
         <v>48</v>
       </c>
@@ -12752,7 +12752,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="n">
         <v>49</v>
       </c>
@@ -12772,7 +12772,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="n">
         <v>50</v>
       </c>
@@ -12811,13 +12811,13 @@
   <dimension ref="A1:G506"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12843,7 +12843,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
@@ -12866,7 +12866,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
@@ -12889,7 +12889,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
@@ -12912,7 +12912,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
@@ -12935,7 +12935,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
@@ -12958,7 +12958,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
@@ -12981,7 +12981,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
@@ -13004,7 +13004,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
@@ -13027,7 +13027,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
@@ -13050,7 +13050,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
@@ -13073,7 +13073,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="n">
         <v>11</v>
       </c>
@@ -13096,7 +13096,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="n">
         <v>12</v>
       </c>
@@ -13119,7 +13119,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="n">
         <v>13</v>
       </c>
@@ -13142,7 +13142,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="n">
         <v>14</v>
       </c>
@@ -13165,7 +13165,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="n">
         <v>15</v>
       </c>
@@ -13188,7 +13188,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="n">
         <v>16</v>
       </c>
@@ -13211,7 +13211,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="n">
         <v>17</v>
       </c>
@@ -13234,7 +13234,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="n">
         <v>18</v>
       </c>
@@ -13257,7 +13257,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="n">
         <v>19</v>
       </c>
@@ -13280,7 +13280,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="n">
         <v>20</v>
       </c>
@@ -13303,7 +13303,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="n">
         <v>21</v>
       </c>
@@ -13326,7 +13326,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="n">
         <v>22</v>
       </c>
@@ -13349,7 +13349,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="n">
         <v>23</v>
       </c>
@@ -13372,7 +13372,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="n">
         <v>24</v>
       </c>
@@ -13395,7 +13395,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="n">
         <v>25</v>
       </c>
@@ -13418,7 +13418,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="n">
         <v>26</v>
       </c>
@@ -13441,7 +13441,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="n">
         <v>27</v>
       </c>
@@ -13464,7 +13464,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="n">
         <v>28</v>
       </c>
@@ -13487,7 +13487,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="n">
         <v>29</v>
       </c>
@@ -13510,7 +13510,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="n">
         <v>30</v>
       </c>
@@ -13533,7 +13533,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="n">
         <v>31</v>
       </c>
@@ -13556,7 +13556,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="n">
         <v>32</v>
       </c>
@@ -13579,7 +13579,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="n">
         <v>33</v>
       </c>
@@ -13602,7 +13602,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="n">
         <v>34</v>
       </c>
@@ -13625,7 +13625,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="n">
         <v>35</v>
       </c>
@@ -13648,7 +13648,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="n">
         <v>36</v>
       </c>
@@ -13671,7 +13671,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="n">
         <v>37</v>
       </c>
@@ -13694,7 +13694,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="n">
         <v>38</v>
       </c>
@@ -13717,7 +13717,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="n">
         <v>39</v>
       </c>
@@ -13740,7 +13740,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="n">
         <v>40</v>
       </c>
@@ -13763,7 +13763,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="n">
         <v>41</v>
       </c>
@@ -13786,7 +13786,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="n">
         <v>42</v>
       </c>
@@ -13809,7 +13809,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="n">
         <v>43</v>
       </c>
@@ -13832,7 +13832,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="n">
         <v>44</v>
       </c>
@@ -13855,7 +13855,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="n">
         <v>45</v>
       </c>
@@ -13878,7 +13878,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="n">
         <v>46</v>
       </c>
@@ -13901,7 +13901,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="n">
         <v>47</v>
       </c>
@@ -13924,7 +13924,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="n">
         <v>48</v>
       </c>
@@ -13947,7 +13947,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="n">
         <v>49</v>
       </c>
@@ -13970,7 +13970,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="n">
         <v>50</v>
       </c>
@@ -13993,7 +13993,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="n">
         <v>51</v>
       </c>
@@ -14016,7 +14016,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="n">
         <v>52</v>
       </c>
@@ -14039,7 +14039,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="n">
         <v>53</v>
       </c>
@@ -14062,7 +14062,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="n">
         <v>54</v>
       </c>
@@ -14085,7 +14085,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="n">
         <v>55</v>
       </c>
@@ -14108,7 +14108,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="n">
         <v>56</v>
       </c>
@@ -14131,7 +14131,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="n">
         <v>57</v>
       </c>
@@ -14154,7 +14154,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="n">
         <v>58</v>
       </c>
@@ -14177,7 +14177,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="n">
         <v>59</v>
       </c>
@@ -14200,7 +14200,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="n">
         <v>60</v>
       </c>
@@ -14223,7 +14223,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="n">
         <v>61</v>
       </c>
@@ -14246,7 +14246,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="n">
         <v>62</v>
       </c>
@@ -14269,7 +14269,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="n">
         <v>63</v>
       </c>
@@ -14292,7 +14292,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="n">
         <v>64</v>
       </c>
@@ -14315,7 +14315,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="n">
         <v>65</v>
       </c>
@@ -14338,7 +14338,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="n">
         <v>66</v>
       </c>
@@ -14361,7 +14361,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="n">
         <v>67</v>
       </c>
@@ -14384,7 +14384,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="3" t="n">
         <v>68</v>
       </c>
@@ -14407,7 +14407,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="n">
         <v>69</v>
       </c>
@@ -14430,7 +14430,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="n">
         <v>70</v>
       </c>
@@ -14453,7 +14453,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="3" t="n">
         <v>71</v>
       </c>
@@ -14476,7 +14476,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="n">
         <v>72</v>
       </c>
@@ -14499,7 +14499,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="3" t="n">
         <v>73</v>
       </c>
@@ -14522,7 +14522,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="n">
         <v>74</v>
       </c>
@@ -14545,7 +14545,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="n">
         <v>75</v>
       </c>
@@ -14568,7 +14568,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="n">
         <v>76</v>
       </c>
@@ -14591,7 +14591,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="n">
         <v>77</v>
       </c>
@@ -14614,7 +14614,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="3" t="n">
         <v>78</v>
       </c>
@@ -14637,7 +14637,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="3" t="n">
         <v>79</v>
       </c>
@@ -14660,7 +14660,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="3" t="n">
         <v>80</v>
       </c>
@@ -14683,7 +14683,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="n">
         <v>81</v>
       </c>
@@ -14706,7 +14706,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="n">
         <v>82</v>
       </c>
@@ -14729,7 +14729,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="3" t="n">
         <v>83</v>
       </c>
@@ -14752,7 +14752,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="3" t="n">
         <v>84</v>
       </c>
@@ -14775,7 +14775,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="3" t="n">
         <v>85</v>
       </c>
@@ -14798,7 +14798,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="3" t="n">
         <v>86</v>
       </c>
@@ -14821,7 +14821,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="3" t="n">
         <v>87</v>
       </c>
@@ -14844,7 +14844,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="3" t="n">
         <v>88</v>
       </c>
@@ -14867,7 +14867,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="3" t="n">
         <v>89</v>
       </c>
@@ -14890,7 +14890,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="3" t="n">
         <v>90</v>
       </c>
@@ -14913,7 +14913,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="3" t="n">
         <v>91</v>
       </c>
@@ -14936,7 +14936,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="3" t="n">
         <v>92</v>
       </c>
@@ -14959,7 +14959,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="3" t="n">
         <v>93</v>
       </c>
@@ -14982,7 +14982,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="3" t="n">
         <v>94</v>
       </c>
@@ -15005,7 +15005,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="3" t="n">
         <v>95</v>
       </c>
@@ -15028,7 +15028,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="3" t="n">
         <v>96</v>
       </c>
@@ -15051,7 +15051,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="3" t="n">
         <v>97</v>
       </c>
@@ -15074,7 +15074,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="3" t="n">
         <v>98</v>
       </c>
@@ -15097,7 +15097,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="3" t="n">
         <v>99</v>
       </c>
@@ -15120,7 +15120,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="3" t="n">
         <v>100</v>
       </c>
@@ -15143,7 +15143,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="3" t="n">
         <v>101</v>
       </c>
@@ -15166,7 +15166,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="3" t="n">
         <v>102</v>
       </c>
@@ -15189,7 +15189,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="3" t="n">
         <v>103</v>
       </c>
@@ -15212,7 +15212,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="3" t="n">
         <v>104</v>
       </c>
@@ -15235,7 +15235,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="3" t="n">
         <v>105</v>
       </c>
@@ -15258,7 +15258,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="3" t="n">
         <v>106</v>
       </c>
@@ -15281,7 +15281,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="3" t="n">
         <v>107</v>
       </c>
@@ -15304,7 +15304,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="3" t="n">
         <v>108</v>
       </c>
@@ -15327,7 +15327,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="3" t="n">
         <v>109</v>
       </c>
@@ -15350,7 +15350,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="3" t="n">
         <v>110</v>
       </c>
@@ -15373,7 +15373,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="3" t="n">
         <v>111</v>
       </c>
@@ -15396,7 +15396,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="3" t="n">
         <v>112</v>
       </c>
@@ -15419,7 +15419,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="3" t="n">
         <v>113</v>
       </c>
@@ -15442,7 +15442,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="3" t="n">
         <v>114</v>
       </c>
@@ -15465,7 +15465,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="3" t="n">
         <v>115</v>
       </c>
@@ -15488,7 +15488,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="3" t="n">
         <v>116</v>
       </c>
@@ -15511,7 +15511,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="3" t="n">
         <v>117</v>
       </c>
@@ -15534,7 +15534,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="3" t="n">
         <v>118</v>
       </c>
@@ -15557,7 +15557,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="3" t="n">
         <v>119</v>
       </c>
@@ -15580,7 +15580,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="3" t="n">
         <v>120</v>
       </c>
@@ -15603,7 +15603,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="3" t="n">
         <v>121</v>
       </c>
@@ -15626,7 +15626,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="3" t="n">
         <v>122</v>
       </c>
@@ -15649,7 +15649,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="3" t="n">
         <v>123</v>
       </c>
@@ -15672,7 +15672,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="3" t="n">
         <v>124</v>
       </c>
@@ -15695,7 +15695,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="3" t="n">
         <v>125</v>
       </c>
@@ -15718,7 +15718,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="3" t="n">
         <v>126</v>
       </c>
@@ -15741,7 +15741,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="3" t="n">
         <v>127</v>
       </c>
@@ -15764,7 +15764,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="3" t="n">
         <v>128</v>
       </c>
@@ -15787,7 +15787,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="3" t="n">
         <v>129</v>
       </c>
@@ -15810,7 +15810,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="3" t="n">
         <v>130</v>
       </c>
@@ -15833,7 +15833,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="3" t="n">
         <v>131</v>
       </c>
@@ -15856,7 +15856,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="3" t="n">
         <v>132</v>
       </c>
@@ -15879,7 +15879,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="3" t="n">
         <v>133</v>
       </c>
@@ -15902,7 +15902,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="3" t="n">
         <v>134</v>
       </c>
@@ -15925,7 +15925,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="3" t="n">
         <v>135</v>
       </c>
@@ -15948,7 +15948,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="3" t="n">
         <v>136</v>
       </c>
@@ -15971,7 +15971,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="3" t="n">
         <v>137</v>
       </c>
@@ -15994,7 +15994,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="3" t="n">
         <v>138</v>
       </c>
@@ -16017,7 +16017,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="3" t="n">
         <v>139</v>
       </c>
@@ -16040,7 +16040,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="3" t="n">
         <v>140</v>
       </c>
@@ -16063,7 +16063,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="3" t="n">
         <v>141</v>
       </c>
@@ -16086,7 +16086,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="3" t="n">
         <v>142</v>
       </c>
@@ -16109,7 +16109,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="3" t="n">
         <v>143</v>
       </c>
@@ -16132,7 +16132,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="3" t="n">
         <v>144</v>
       </c>
@@ -16155,7 +16155,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="3" t="n">
         <v>145</v>
       </c>
@@ -16178,7 +16178,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="3" t="n">
         <v>146</v>
       </c>
@@ -16201,7 +16201,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="3" t="n">
         <v>147</v>
       </c>
@@ -16224,7 +16224,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="3" t="n">
         <v>148</v>
       </c>
@@ -16247,7 +16247,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="3" t="n">
         <v>149</v>
       </c>
@@ -16270,7 +16270,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="3" t="n">
         <v>150</v>
       </c>
@@ -16293,7 +16293,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="3" t="n">
         <v>151</v>
       </c>
@@ -16316,7 +16316,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="3" t="n">
         <v>152</v>
       </c>
@@ -16339,7 +16339,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="3" t="n">
         <v>153</v>
       </c>
@@ -16362,7 +16362,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="3" t="n">
         <v>154</v>
       </c>
@@ -16385,7 +16385,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="3" t="n">
         <v>155</v>
       </c>
@@ -16408,7 +16408,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="3" t="n">
         <v>156</v>
       </c>
@@ -16431,7 +16431,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="3" t="n">
         <v>157</v>
       </c>
@@ -16454,7 +16454,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="3" t="n">
         <v>158</v>
       </c>
@@ -16477,7 +16477,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="3" t="n">
         <v>159</v>
       </c>
@@ -16500,7 +16500,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="3" t="n">
         <v>160</v>
       </c>
@@ -16523,7 +16523,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="3" t="n">
         <v>161</v>
       </c>
@@ -16546,7 +16546,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="3" t="n">
         <v>162</v>
       </c>
@@ -16569,7 +16569,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="3" t="n">
         <v>163</v>
       </c>
@@ -16592,7 +16592,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="3" t="n">
         <v>164</v>
       </c>
@@ -16615,7 +16615,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="3" t="n">
         <v>165</v>
       </c>
@@ -16638,7 +16638,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="3" t="n">
         <v>166</v>
       </c>
@@ -16661,7 +16661,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="3" t="n">
         <v>167</v>
       </c>
@@ -16684,7 +16684,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="3" t="n">
         <v>168</v>
       </c>
@@ -16707,7 +16707,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="3" t="n">
         <v>169</v>
       </c>
@@ -16730,7 +16730,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="3" t="n">
         <v>170</v>
       </c>
@@ -16753,7 +16753,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="3" t="n">
         <v>171</v>
       </c>
@@ -16776,7 +16776,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="3" t="n">
         <v>172</v>
       </c>
@@ -16799,7 +16799,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="3" t="n">
         <v>173</v>
       </c>
@@ -16822,7 +16822,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="3" t="n">
         <v>174</v>
       </c>
@@ -16845,7 +16845,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="3" t="n">
         <v>175</v>
       </c>
@@ -16868,7 +16868,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="3" t="n">
         <v>176</v>
       </c>
@@ -16891,7 +16891,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="3" t="n">
         <v>177</v>
       </c>
@@ -16914,7 +16914,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="3" t="n">
         <v>178</v>
       </c>
@@ -16937,7 +16937,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="3" t="n">
         <v>179</v>
       </c>
@@ -16960,7 +16960,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="3" t="n">
         <v>180</v>
       </c>
@@ -16983,7 +16983,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="3" t="n">
         <v>181</v>
       </c>
@@ -17006,7 +17006,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="3" t="n">
         <v>182</v>
       </c>
@@ -17029,7 +17029,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="3" t="n">
         <v>183</v>
       </c>
@@ -17052,7 +17052,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="3" t="n">
         <v>184</v>
       </c>
@@ -17075,7 +17075,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="3" t="n">
         <v>185</v>
       </c>
@@ -17098,7 +17098,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="3" t="n">
         <v>186</v>
       </c>
@@ -17121,7 +17121,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="3" t="n">
         <v>187</v>
       </c>
@@ -17144,7 +17144,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="3" t="n">
         <v>188</v>
       </c>
@@ -17167,7 +17167,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="3" t="n">
         <v>189</v>
       </c>
@@ -17190,7 +17190,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="3" t="n">
         <v>190</v>
       </c>
@@ -17213,7 +17213,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="3" t="n">
         <v>191</v>
       </c>
@@ -17236,7 +17236,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="3" t="n">
         <v>192</v>
       </c>
@@ -17259,7 +17259,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="3" t="n">
         <v>193</v>
       </c>
@@ -17282,7 +17282,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="3" t="n">
         <v>194</v>
       </c>
@@ -17305,7 +17305,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="3" t="n">
         <v>195</v>
       </c>
@@ -17328,7 +17328,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="3" t="n">
         <v>196</v>
       </c>
@@ -17351,7 +17351,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="3" t="n">
         <v>197</v>
       </c>
@@ -17374,7 +17374,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="3" t="n">
         <v>198</v>
       </c>
@@ -17397,7 +17397,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="3" t="n">
         <v>199</v>
       </c>
@@ -17420,7 +17420,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="3" t="n">
         <v>200</v>
       </c>
@@ -17443,7 +17443,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="202" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="3" t="n">
         <v>201</v>
       </c>
@@ -17466,7 +17466,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="3" t="n">
         <v>202</v>
       </c>
@@ -17489,7 +17489,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="3" t="n">
         <v>203</v>
       </c>
@@ -17512,7 +17512,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="3" t="n">
         <v>204</v>
       </c>
@@ -17535,7 +17535,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="206" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="3" t="n">
         <v>205</v>
       </c>
@@ -17558,7 +17558,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="207" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="3" t="n">
         <v>206</v>
       </c>
@@ -17581,7 +17581,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="208" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="3" t="n">
         <v>207</v>
       </c>
@@ -17604,7 +17604,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="209" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="3" t="n">
         <v>208</v>
       </c>
@@ -17627,7 +17627,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="210" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="3" t="n">
         <v>209</v>
       </c>
@@ -17650,7 +17650,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="211" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="3" t="n">
         <v>210</v>
       </c>
@@ -17673,7 +17673,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="212" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="212" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="3" t="n">
         <v>211</v>
       </c>
@@ -17696,7 +17696,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="3" t="n">
         <v>212</v>
       </c>
@@ -17719,7 +17719,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="214" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="214" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="3" t="n">
         <v>213</v>
       </c>
@@ -17742,7 +17742,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="215" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="215" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="3" t="n">
         <v>214</v>
       </c>
@@ -17765,7 +17765,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="216" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="216" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="3" t="n">
         <v>215</v>
       </c>
@@ -17788,7 +17788,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="217" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="217" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="3" t="n">
         <v>216</v>
       </c>
@@ -17811,7 +17811,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="218" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="218" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="3" t="n">
         <v>217</v>
       </c>
@@ -17834,7 +17834,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="219" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="219" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="3" t="n">
         <v>218</v>
       </c>
@@ -17857,7 +17857,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="220" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="220" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="3" t="n">
         <v>219</v>
       </c>
@@ -17880,7 +17880,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="3" t="n">
         <v>220</v>
       </c>
@@ -17903,7 +17903,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="3" t="n">
         <v>221</v>
       </c>
@@ -17926,7 +17926,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="223" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="223" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="3" t="n">
         <v>222</v>
       </c>
@@ -17949,7 +17949,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="224" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="224" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="3" t="n">
         <v>223</v>
       </c>
@@ -17972,7 +17972,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="225" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="3" t="n">
         <v>224</v>
       </c>
@@ -17995,7 +17995,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="226" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="3" t="n">
         <v>225</v>
       </c>
@@ -18018,7 +18018,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="227" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="227" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="3" t="n">
         <v>226</v>
       </c>
@@ -18041,7 +18041,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="228" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="228" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="3" t="n">
         <v>227</v>
       </c>
@@ -18064,7 +18064,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="229" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="229" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="3" t="n">
         <v>228</v>
       </c>
@@ -18087,7 +18087,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="230" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="230" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="3" t="n">
         <v>229</v>
       </c>
@@ -18110,7 +18110,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="231" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="231" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="3" t="n">
         <v>230</v>
       </c>
@@ -18133,7 +18133,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="232" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="232" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="3" t="n">
         <v>231</v>
       </c>
@@ -18156,7 +18156,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="233" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="233" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="3" t="n">
         <v>232</v>
       </c>
@@ -18179,7 +18179,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="234" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="234" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="3" t="n">
         <v>233</v>
       </c>
@@ -18202,7 +18202,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="235" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="235" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="3" t="n">
         <v>234</v>
       </c>
@@ -18225,7 +18225,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="236" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="236" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="3" t="n">
         <v>235</v>
       </c>
@@ -18248,7 +18248,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="237" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="237" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="3" t="n">
         <v>236</v>
       </c>
@@ -18271,7 +18271,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="238" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="238" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="3" t="n">
         <v>237</v>
       </c>
@@ -18294,7 +18294,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="239" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="239" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="3" t="n">
         <v>238</v>
       </c>
@@ -18317,7 +18317,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="240" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="3" t="n">
         <v>239</v>
       </c>
@@ -18340,7 +18340,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="241" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="241" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="3" t="n">
         <v>240</v>
       </c>
@@ -18363,7 +18363,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="242" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="242" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="3" t="n">
         <v>241</v>
       </c>
@@ -18386,7 +18386,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="243" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="243" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="3" t="n">
         <v>242</v>
       </c>
@@ -18409,7 +18409,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="244" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="244" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="3" t="n">
         <v>243</v>
       </c>
@@ -18432,7 +18432,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="245" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="245" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="3" t="n">
         <v>244</v>
       </c>
@@ -18455,7 +18455,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="246" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="246" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="3" t="n">
         <v>245</v>
       </c>
@@ -18478,7 +18478,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="247" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="247" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="3" t="n">
         <v>246</v>
       </c>
@@ -18501,7 +18501,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="248" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="248" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="3" t="n">
         <v>247</v>
       </c>
@@ -18524,7 +18524,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="249" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="249" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="3" t="n">
         <v>248</v>
       </c>
@@ -18547,7 +18547,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="250" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="250" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="3" t="n">
         <v>249</v>
       </c>
@@ -18570,7 +18570,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="251" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="251" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="3" t="n">
         <v>250</v>
       </c>
@@ -18593,7 +18593,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="252" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="252" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="3" t="n">
         <v>251</v>
       </c>
@@ -18616,7 +18616,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="253" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="253" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="3" t="n">
         <v>252</v>
       </c>
@@ -18639,7 +18639,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="254" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="254" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="3" t="n">
         <v>253</v>
       </c>
@@ -18662,7 +18662,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="255" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="255" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="3" t="n">
         <v>254</v>
       </c>
@@ -18685,7 +18685,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="256" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="256" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="3" t="n">
         <v>255</v>
       </c>
@@ -18708,7 +18708,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="257" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="257" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="3" t="n">
         <v>256</v>
       </c>
@@ -18731,7 +18731,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="258" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="258" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="3" t="n">
         <v>257</v>
       </c>
@@ -18754,7 +18754,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="259" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="259" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="3" t="n">
         <v>258</v>
       </c>
@@ -18777,7 +18777,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="260" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="260" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="3" t="n">
         <v>259</v>
       </c>
@@ -18800,7 +18800,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="261" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="261" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="3" t="n">
         <v>260</v>
       </c>
@@ -18823,7 +18823,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="262" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="262" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="3" t="n">
         <v>261</v>
       </c>
@@ -18846,7 +18846,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="263" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="263" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="3" t="n">
         <v>262</v>
       </c>
@@ -18869,7 +18869,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="264" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="264" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="3" t="n">
         <v>263</v>
       </c>
@@ -18892,7 +18892,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="265" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="265" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="3" t="n">
         <v>264</v>
       </c>
@@ -18915,7 +18915,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="266" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="266" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="3" t="n">
         <v>265</v>
       </c>
@@ -18938,7 +18938,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="267" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="267" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="3" t="n">
         <v>266</v>
       </c>
@@ -18961,7 +18961,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="268" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="268" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="3" t="n">
         <v>267</v>
       </c>
@@ -18984,7 +18984,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="269" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="269" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="3" t="n">
         <v>268</v>
       </c>
@@ -19007,7 +19007,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="270" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="270" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="3" t="n">
         <v>269</v>
       </c>
@@ -19030,7 +19030,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="271" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="271" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="3" t="n">
         <v>270</v>
       </c>
@@ -19053,7 +19053,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="272" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="272" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="3" t="n">
         <v>271</v>
       </c>
@@ -19076,7 +19076,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="273" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="273" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="3" t="n">
         <v>272</v>
       </c>
@@ -19099,7 +19099,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="274" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="274" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="3" t="n">
         <v>273</v>
       </c>
@@ -19122,7 +19122,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="275" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="275" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="3" t="n">
         <v>274</v>
       </c>
@@ -19145,7 +19145,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="276" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="276" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="3" t="n">
         <v>275</v>
       </c>
@@ -19168,7 +19168,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="277" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="277" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="3" t="n">
         <v>276</v>
       </c>
@@ -19191,7 +19191,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="278" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="278" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="3" t="n">
         <v>277</v>
       </c>
@@ -19214,7 +19214,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="279" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="279" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="3" t="n">
         <v>278</v>
       </c>
@@ -19237,7 +19237,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="280" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="280" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="3" t="n">
         <v>279</v>
       </c>
@@ -19260,7 +19260,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="281" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="281" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="3" t="n">
         <v>280</v>
       </c>
@@ -19283,7 +19283,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="282" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="282" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="3" t="n">
         <v>281</v>
       </c>
@@ -19306,7 +19306,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="283" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="283" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="3" t="n">
         <v>282</v>
       </c>
@@ -19329,7 +19329,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="284" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="284" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="3" t="n">
         <v>283</v>
       </c>
@@ -19352,7 +19352,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="285" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="285" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="3" t="n">
         <v>284</v>
       </c>
@@ -19375,7 +19375,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="286" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="286" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="3" t="n">
         <v>285</v>
       </c>
@@ -19398,7 +19398,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="287" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="287" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="3" t="n">
         <v>286</v>
       </c>
@@ -19421,7 +19421,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="288" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="288" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="3" t="n">
         <v>287</v>
       </c>
@@ -19444,7 +19444,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="289" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="289" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="3" t="n">
         <v>288</v>
       </c>
@@ -19467,7 +19467,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="290" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="290" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="3" t="n">
         <v>289</v>
       </c>
@@ -19490,7 +19490,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="291" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="291" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="3" t="n">
         <v>290</v>
       </c>
@@ -19513,7 +19513,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="292" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="292" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="3" t="n">
         <v>291</v>
       </c>
@@ -19536,7 +19536,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="293" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="293" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="3" t="n">
         <v>292</v>
       </c>
@@ -19559,7 +19559,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="294" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="294" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="3" t="n">
         <v>293</v>
       </c>
@@ -19582,7 +19582,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="295" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="295" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="3" t="n">
         <v>294</v>
       </c>
@@ -19605,7 +19605,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="296" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="296" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="3" t="n">
         <v>295</v>
       </c>
@@ -19628,7 +19628,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="297" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="297" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="3" t="n">
         <v>296</v>
       </c>
@@ -19651,7 +19651,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="298" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="298" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="3" t="n">
         <v>297</v>
       </c>
@@ -19674,7 +19674,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="299" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="299" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="3" t="n">
         <v>298</v>
       </c>
@@ -19697,7 +19697,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="300" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="300" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="3" t="n">
         <v>299</v>
       </c>
@@ -19720,7 +19720,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="301" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="301" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="3" t="n">
         <v>300</v>
       </c>
@@ -19743,7 +19743,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="302" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="302" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="3" t="n">
         <v>301</v>
       </c>
@@ -19766,7 +19766,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="303" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="303" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="3" t="n">
         <v>302</v>
       </c>
@@ -19789,7 +19789,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="304" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="304" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="3" t="n">
         <v>303</v>
       </c>
@@ -19812,7 +19812,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="305" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="305" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="3" t="n">
         <v>304</v>
       </c>
@@ -19835,7 +19835,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="306" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="306" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="3" t="n">
         <v>305</v>
       </c>
@@ -19858,7 +19858,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="307" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="307" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="3" t="n">
         <v>306</v>
       </c>
@@ -19881,7 +19881,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="308" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="308" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="3" t="n">
         <v>307</v>
       </c>
@@ -19904,7 +19904,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="309" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="309" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="3" t="n">
         <v>308</v>
       </c>
@@ -19927,7 +19927,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="310" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="310" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="3" t="n">
         <v>309</v>
       </c>
@@ -19950,7 +19950,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="311" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="311" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="3" t="n">
         <v>310</v>
       </c>
@@ -19973,7 +19973,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="312" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="312" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="3" t="n">
         <v>311</v>
       </c>
@@ -19996,7 +19996,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="313" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="313" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="3" t="n">
         <v>312</v>
       </c>
@@ -20019,7 +20019,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="314" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="314" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="3" t="n">
         <v>313</v>
       </c>
@@ -20042,7 +20042,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="315" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="315" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="3" t="n">
         <v>314</v>
       </c>
@@ -20065,7 +20065,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="316" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="316" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="3" t="n">
         <v>315</v>
       </c>
@@ -20088,7 +20088,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="317" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="317" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="3" t="n">
         <v>316</v>
       </c>
@@ -20111,7 +20111,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="318" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="318" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="3" t="n">
         <v>317</v>
       </c>
@@ -20134,7 +20134,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="319" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="319" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="3" t="n">
         <v>318</v>
       </c>
@@ -20157,7 +20157,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="320" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="320" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="3" t="n">
         <v>319</v>
       </c>
@@ -20180,7 +20180,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="321" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="321" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="3" t="n">
         <v>320</v>
       </c>
@@ -20203,7 +20203,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="322" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="322" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="3" t="n">
         <v>321</v>
       </c>
@@ -20226,7 +20226,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="323" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="323" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="3" t="n">
         <v>322</v>
       </c>
@@ -20249,7 +20249,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="324" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="324" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="3" t="n">
         <v>323</v>
       </c>
@@ -20272,7 +20272,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="325" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="325" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="3" t="n">
         <v>324</v>
       </c>
@@ -20295,7 +20295,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="326" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="326" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="3" t="n">
         <v>325</v>
       </c>
@@ -20318,7 +20318,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="327" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="327" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="3" t="n">
         <v>326</v>
       </c>
@@ -20341,7 +20341,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="328" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="328" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="3" t="n">
         <v>327</v>
       </c>
@@ -20364,7 +20364,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="329" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="329" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="3" t="n">
         <v>328</v>
       </c>
@@ -20387,7 +20387,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="330" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="330" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="3" t="n">
         <v>329</v>
       </c>
@@ -20410,7 +20410,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="331" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="331" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="3" t="n">
         <v>330</v>
       </c>
@@ -20433,7 +20433,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="332" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="332" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="3" t="n">
         <v>331</v>
       </c>
@@ -20456,7 +20456,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="333" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="333" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="3" t="n">
         <v>332</v>
       </c>
@@ -20479,7 +20479,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="334" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="334" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="3" t="n">
         <v>333</v>
       </c>
@@ -20502,7 +20502,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="335" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="335" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="3" t="n">
         <v>334</v>
       </c>
@@ -20525,7 +20525,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="336" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="336" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="3" t="n">
         <v>335</v>
       </c>
@@ -20548,7 +20548,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="337" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="337" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="3" t="n">
         <v>336</v>
       </c>
@@ -20571,7 +20571,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="338" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="338" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="3" t="n">
         <v>337</v>
       </c>
@@ -20594,7 +20594,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="339" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="339" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="3" t="n">
         <v>338</v>
       </c>
@@ -20617,7 +20617,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="340" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="340" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="3" t="n">
         <v>339</v>
       </c>
@@ -20640,7 +20640,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="341" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="341" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="3" t="n">
         <v>340</v>
       </c>
@@ -20663,7 +20663,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="342" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="342" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="3" t="n">
         <v>341</v>
       </c>
@@ -20686,7 +20686,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="343" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="343" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="3" t="n">
         <v>342</v>
       </c>
@@ -20709,7 +20709,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="344" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="344" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="3" t="n">
         <v>343</v>
       </c>
@@ -20732,7 +20732,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="345" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="345" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="3" t="n">
         <v>344</v>
       </c>
@@ -20755,7 +20755,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="346" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="346" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="3" t="n">
         <v>345</v>
       </c>
@@ -20778,7 +20778,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="347" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="347" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="3" t="n">
         <v>346</v>
       </c>
@@ -20801,7 +20801,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="348" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="348" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="3" t="n">
         <v>347</v>
       </c>
@@ -20824,7 +20824,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="349" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="349" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="3" t="n">
         <v>348</v>
       </c>
@@ -20847,7 +20847,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="350" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="350" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="3" t="n">
         <v>349</v>
       </c>
@@ -20870,7 +20870,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="351" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="351" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="3" t="n">
         <v>350</v>
       </c>
@@ -20893,7 +20893,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="352" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="352" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="3" t="n">
         <v>351</v>
       </c>
@@ -20916,7 +20916,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="353" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="353" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="3" t="n">
         <v>352</v>
       </c>
@@ -20939,7 +20939,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="354" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="354" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="3" t="n">
         <v>353</v>
       </c>
@@ -20962,7 +20962,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="355" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="355" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="3" t="n">
         <v>354</v>
       </c>
@@ -20985,7 +20985,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="356" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="356" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="3" t="n">
         <v>355</v>
       </c>
@@ -21008,7 +21008,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="357" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="357" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="3" t="n">
         <v>356</v>
       </c>
@@ -21031,7 +21031,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="358" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="358" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="3" t="n">
         <v>357</v>
       </c>
@@ -21054,7 +21054,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="359" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="359" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="3" t="n">
         <v>358</v>
       </c>
@@ -21077,7 +21077,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="360" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="360" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="3" t="n">
         <v>359</v>
       </c>
@@ -21100,7 +21100,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="361" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="361" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="3" t="n">
         <v>360</v>
       </c>
@@ -21123,7 +21123,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="362" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="362" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="3" t="n">
         <v>361</v>
       </c>
@@ -21146,7 +21146,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="363" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="363" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="3" t="n">
         <v>362</v>
       </c>
@@ -21169,7 +21169,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="364" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="364" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="3" t="n">
         <v>363</v>
       </c>
@@ -21192,7 +21192,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="365" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="365" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="3" t="n">
         <v>364</v>
       </c>
@@ -21215,7 +21215,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="366" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="366" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="3" t="n">
         <v>365</v>
       </c>
@@ -21238,7 +21238,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="367" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="367" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="3" t="n">
         <v>366</v>
       </c>
@@ -21261,7 +21261,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="368" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="368" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A368" s="3" t="n">
         <v>367</v>
       </c>
@@ -21284,7 +21284,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="369" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="369" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="3" t="n">
         <v>368</v>
       </c>
@@ -21307,7 +21307,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="370" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="370" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="3" t="n">
         <v>369</v>
       </c>
@@ -21330,7 +21330,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="371" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="371" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="3" t="n">
         <v>370</v>
       </c>
@@ -21353,7 +21353,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="372" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="372" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="3" t="n">
         <v>371</v>
       </c>
@@ -21376,7 +21376,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="373" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="373" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="3" t="n">
         <v>372</v>
       </c>
@@ -21399,7 +21399,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="374" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="374" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="3" t="n">
         <v>373</v>
       </c>
@@ -21422,7 +21422,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="375" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="375" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="3" t="n">
         <v>374</v>
       </c>
@@ -21445,7 +21445,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="376" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="376" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="3" t="n">
         <v>375</v>
       </c>
@@ -21468,7 +21468,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="377" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="377" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="3" t="n">
         <v>376</v>
       </c>
@@ -21491,7 +21491,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="378" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="378" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="3" t="n">
         <v>377</v>
       </c>
@@ -21514,7 +21514,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="379" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="379" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="3" t="n">
         <v>378</v>
       </c>
@@ -21537,7 +21537,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="380" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="380" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="3" t="n">
         <v>379</v>
       </c>
@@ -21560,7 +21560,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="381" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="381" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="3" t="n">
         <v>380</v>
       </c>
@@ -21583,7 +21583,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="382" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="382" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="3" t="n">
         <v>381</v>
       </c>
@@ -21606,7 +21606,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="383" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="383" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="3" t="n">
         <v>382</v>
       </c>
@@ -21629,7 +21629,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="384" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="384" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="3" t="n">
         <v>383</v>
       </c>
@@ -21652,7 +21652,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="385" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="385" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="3" t="n">
         <v>384</v>
       </c>
@@ -21675,7 +21675,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="386" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="386" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="3" t="n">
         <v>385</v>
       </c>
@@ -21698,7 +21698,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="387" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="387" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="3" t="n">
         <v>386</v>
       </c>
@@ -21721,7 +21721,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="388" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="388" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="3" t="n">
         <v>387</v>
       </c>
@@ -21744,7 +21744,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="389" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="389" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="3" t="n">
         <v>388</v>
       </c>
@@ -21767,7 +21767,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="390" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="390" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="3" t="n">
         <v>389</v>
       </c>
@@ -21790,7 +21790,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="391" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="391" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="3" t="n">
         <v>390</v>
       </c>
@@ -21813,7 +21813,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="392" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="392" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="3" t="n">
         <v>391</v>
       </c>
@@ -21836,7 +21836,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="393" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="393" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="3" t="n">
         <v>392</v>
       </c>
@@ -21859,7 +21859,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="394" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="394" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="3" t="n">
         <v>393</v>
       </c>
@@ -21882,7 +21882,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="395" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="395" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="3" t="n">
         <v>394</v>
       </c>
@@ -21905,7 +21905,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="396" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="396" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="3" t="n">
         <v>395</v>
       </c>
@@ -21928,7 +21928,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="397" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="397" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="3" t="n">
         <v>396</v>
       </c>
@@ -21951,7 +21951,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="398" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="398" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="3" t="n">
         <v>397</v>
       </c>
@@ -21974,7 +21974,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="399" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="399" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="3" t="n">
         <v>398</v>
       </c>
@@ -21997,7 +21997,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="400" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="400" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="3" t="n">
         <v>399</v>
       </c>
@@ -22020,7 +22020,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="401" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="401" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="3" t="n">
         <v>400</v>
       </c>
@@ -22043,7 +22043,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="402" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="402" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="3" t="n">
         <v>401</v>
       </c>
@@ -22066,7 +22066,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="403" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="403" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="3" t="n">
         <v>402</v>
       </c>
@@ -22089,7 +22089,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="404" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="404" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="3" t="n">
         <v>403</v>
       </c>
@@ -22112,7 +22112,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="405" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="405" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="3" t="n">
         <v>404</v>
       </c>
@@ -22135,7 +22135,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="406" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="406" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="3" t="n">
         <v>405</v>
       </c>
@@ -22158,7 +22158,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="407" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="407" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="3" t="n">
         <v>406</v>
       </c>
@@ -22181,7 +22181,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="408" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="408" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="3" t="n">
         <v>407</v>
       </c>
@@ -22204,7 +22204,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="409" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="409" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="3" t="n">
         <v>408</v>
       </c>
@@ -22227,7 +22227,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="410" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="410" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="3" t="n">
         <v>409</v>
       </c>
@@ -22250,7 +22250,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="411" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="411" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="3" t="n">
         <v>410</v>
       </c>
@@ -22273,7 +22273,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="412" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="412" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="3" t="n">
         <v>411</v>
       </c>
@@ -22296,7 +22296,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="413" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="413" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="3" t="n">
         <v>412</v>
       </c>
@@ -22319,7 +22319,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="414" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="414" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="3" t="n">
         <v>413</v>
       </c>
@@ -22342,7 +22342,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="415" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="415" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="3" t="n">
         <v>414</v>
       </c>
@@ -22365,7 +22365,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="416" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="416" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="3" t="n">
         <v>415</v>
       </c>
@@ -22388,7 +22388,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="417" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="417" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="3" t="n">
         <v>416</v>
       </c>
@@ -22411,7 +22411,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="418" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="418" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="3" t="n">
         <v>417</v>
       </c>
@@ -22434,7 +22434,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="419" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="419" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="3" t="n">
         <v>418</v>
       </c>
@@ -22457,7 +22457,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="420" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="420" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="3" t="n">
         <v>419</v>
       </c>
@@ -22480,7 +22480,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="421" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="421" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="3" t="n">
         <v>420</v>
       </c>
@@ -22503,7 +22503,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="422" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="422" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="3" t="n">
         <v>421</v>
       </c>
@@ -22526,7 +22526,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="423" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="423" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="3" t="n">
         <v>422</v>
       </c>
@@ -22549,7 +22549,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="424" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="424" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="3" t="n">
         <v>423</v>
       </c>
@@ -22572,7 +22572,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="425" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="425" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="3" t="n">
         <v>424</v>
       </c>
@@ -22595,7 +22595,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="426" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="426" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="3" t="n">
         <v>425</v>
       </c>
@@ -22618,7 +22618,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="427" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="427" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="3" t="n">
         <v>426</v>
       </c>
@@ -22641,7 +22641,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="428" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="428" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="3" t="n">
         <v>427</v>
       </c>
@@ -22664,7 +22664,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="429" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="429" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="3" t="n">
         <v>428</v>
       </c>
@@ -22687,7 +22687,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="430" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="430" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="3" t="n">
         <v>429</v>
       </c>
@@ -22710,7 +22710,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="431" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="431" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="3" t="n">
         <v>430</v>
       </c>
@@ -22733,7 +22733,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="432" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="432" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="3" t="n">
         <v>431</v>
       </c>
@@ -22756,7 +22756,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="433" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="433" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="3" t="n">
         <v>432</v>
       </c>
@@ -22779,7 +22779,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="434" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="434" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="3" t="n">
         <v>433</v>
       </c>
@@ -22802,7 +22802,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="435" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="435" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="3" t="n">
         <v>434</v>
       </c>
@@ -22825,7 +22825,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="436" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="436" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="3" t="n">
         <v>435</v>
       </c>
@@ -22848,7 +22848,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="437" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="437" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="3" t="n">
         <v>436</v>
       </c>
@@ -22871,7 +22871,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="438" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="438" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="3" t="n">
         <v>437</v>
       </c>
@@ -22894,7 +22894,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="439" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="439" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="3" t="n">
         <v>438</v>
       </c>
@@ -22917,7 +22917,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="440" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="440" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="3" t="n">
         <v>439</v>
       </c>
@@ -22940,7 +22940,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="441" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="441" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="3" t="n">
         <v>440</v>
       </c>
@@ -22963,7 +22963,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="442" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="442" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="3" t="n">
         <v>441</v>
       </c>
@@ -22986,7 +22986,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="443" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="443" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="3" t="n">
         <v>442</v>
       </c>
@@ -23009,7 +23009,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="444" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="444" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="3" t="n">
         <v>443</v>
       </c>
@@ -23032,7 +23032,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="445" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="445" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="3" t="n">
         <v>444</v>
       </c>
@@ -23055,7 +23055,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="446" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="446" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="3" t="n">
         <v>445</v>
       </c>
@@ -23078,7 +23078,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="447" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="447" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="3" t="n">
         <v>446</v>
       </c>
@@ -23101,7 +23101,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="448" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="448" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="3" t="n">
         <v>447</v>
       </c>
@@ -23124,7 +23124,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="449" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="449" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="3" t="n">
         <v>448</v>
       </c>
@@ -23147,7 +23147,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="450" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="450" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="3" t="n">
         <v>449</v>
       </c>
@@ -23170,7 +23170,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="451" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="451" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="3" t="n">
         <v>450</v>
       </c>
@@ -23193,7 +23193,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="452" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="452" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="3" t="n">
         <v>451</v>
       </c>
@@ -23216,7 +23216,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="453" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="453" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="3" t="n">
         <v>452</v>
       </c>
@@ -23239,7 +23239,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="454" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="454" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="3" t="n">
         <v>453</v>
       </c>
@@ -23262,7 +23262,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="455" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="455" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="3" t="n">
         <v>454</v>
       </c>
@@ -23285,7 +23285,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="456" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="456" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="3" t="n">
         <v>455</v>
       </c>
@@ -23308,7 +23308,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="457" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="457" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="3" t="n">
         <v>456</v>
       </c>
@@ -23331,7 +23331,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="458" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="458" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="3" t="n">
         <v>457</v>
       </c>
@@ -23354,7 +23354,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="459" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="459" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="3" t="n">
         <v>458</v>
       </c>
@@ -23377,7 +23377,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="460" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="460" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="3" t="n">
         <v>459</v>
       </c>
@@ -23400,7 +23400,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="461" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="461" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="3" t="n">
         <v>460</v>
       </c>
@@ -23423,7 +23423,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="462" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="462" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="3" t="n">
         <v>461</v>
       </c>
@@ -23446,7 +23446,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="463" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="463" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="3" t="n">
         <v>462</v>
       </c>
@@ -23469,7 +23469,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="464" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="464" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="3" t="n">
         <v>463</v>
       </c>
@@ -23492,7 +23492,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="465" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="465" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="3" t="n">
         <v>464</v>
       </c>
@@ -23515,7 +23515,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="466" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="466" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A466" s="3" t="n">
         <v>465</v>
       </c>
@@ -23538,7 +23538,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="467" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="467" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A467" s="3" t="n">
         <v>466</v>
       </c>
@@ -23561,7 +23561,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="468" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="468" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A468" s="3" t="n">
         <v>467</v>
       </c>
@@ -23584,7 +23584,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="469" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="469" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A469" s="3" t="n">
         <v>468</v>
       </c>
@@ -23607,7 +23607,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="470" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="470" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A470" s="3" t="n">
         <v>469</v>
       </c>
@@ -23630,7 +23630,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="471" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="471" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A471" s="3" t="n">
         <v>470</v>
       </c>
@@ -23653,7 +23653,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="472" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="472" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A472" s="3" t="n">
         <v>471</v>
       </c>
@@ -23676,7 +23676,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="473" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="473" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A473" s="3" t="n">
         <v>472</v>
       </c>
@@ -23699,7 +23699,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="474" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="474" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A474" s="3" t="n">
         <v>473</v>
       </c>
@@ -23722,7 +23722,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="475" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="475" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A475" s="3" t="n">
         <v>474</v>
       </c>
@@ -23745,7 +23745,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="476" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="476" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A476" s="3" t="n">
         <v>475</v>
       </c>
@@ -23768,7 +23768,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="477" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="477" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A477" s="3" t="n">
         <v>476</v>
       </c>
@@ -23791,7 +23791,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="478" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="478" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A478" s="3" t="n">
         <v>477</v>
       </c>
@@ -23814,7 +23814,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="479" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="479" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A479" s="3" t="n">
         <v>478</v>
       </c>
@@ -23837,7 +23837,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="480" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="480" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A480" s="3" t="n">
         <v>479</v>
       </c>
@@ -23860,7 +23860,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="481" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="481" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A481" s="3" t="n">
         <v>480</v>
       </c>
@@ -23883,7 +23883,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="482" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="482" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A482" s="3" t="n">
         <v>481</v>
       </c>
@@ -23906,7 +23906,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="483" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="483" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A483" s="3" t="n">
         <v>482</v>
       </c>
@@ -23929,7 +23929,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="484" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="484" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A484" s="3" t="n">
         <v>483</v>
       </c>
@@ -23952,7 +23952,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="485" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="485" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A485" s="3" t="n">
         <v>484</v>
       </c>
@@ -23975,7 +23975,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="486" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="486" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A486" s="3" t="n">
         <v>485</v>
       </c>
@@ -23998,7 +23998,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="487" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="487" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A487" s="3" t="n">
         <v>486</v>
       </c>
@@ -24021,7 +24021,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="488" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="488" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A488" s="3" t="n">
         <v>487</v>
       </c>
@@ -24044,7 +24044,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="489" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="489" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A489" s="3" t="n">
         <v>488</v>
       </c>
@@ -24067,7 +24067,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="490" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="490" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A490" s="3" t="n">
         <v>489</v>
       </c>
@@ -24090,7 +24090,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="491" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="491" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A491" s="3" t="n">
         <v>490</v>
       </c>
@@ -24113,7 +24113,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="492" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="492" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A492" s="3" t="n">
         <v>491</v>
       </c>
@@ -24136,7 +24136,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="493" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="493" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A493" s="3" t="n">
         <v>492</v>
       </c>
@@ -24159,7 +24159,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="494" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="494" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A494" s="3" t="n">
         <v>493</v>
       </c>
@@ -24182,7 +24182,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="495" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="495" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A495" s="3" t="n">
         <v>494</v>
       </c>
@@ -24205,7 +24205,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="496" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="496" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A496" s="3" t="n">
         <v>495</v>
       </c>
@@ -24228,7 +24228,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="497" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="497" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A497" s="3" t="n">
         <v>496</v>
       </c>
@@ -24251,7 +24251,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="498" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="498" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A498" s="3" t="n">
         <v>497</v>
       </c>
@@ -24274,7 +24274,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="499" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="499" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A499" s="3" t="n">
         <v>498</v>
       </c>
@@ -24297,7 +24297,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="500" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="500" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A500" s="3" t="n">
         <v>499</v>
       </c>
@@ -24320,7 +24320,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="501" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="501" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A501" s="3" t="n">
         <v>500</v>
       </c>
